--- a/EVO_TOTAL_V0.xlsx
+++ b/EVO_TOTAL_V0.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C452F9CB-62D6-8F4A-9593-C70884E89CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37320" yWindow="3120" windowWidth="28800" windowHeight="15820" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33600" yWindow="-980" windowWidth="33600" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Listas" sheetId="16" r:id="rId1"/>
